--- a/EA流程架构项目/_VNW引用原件/D1_价值节点清单_V3.57.xlsx
+++ b/EA流程架构项目/_VNW引用原件/D1_价值节点清单_V3.57.xlsx
@@ -9313,7 +9313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9337,7 +9337,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="14.5" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -9635,8 +9634,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
     <row r="17" ht="16.5" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
@@ -9916,7 +9913,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -10650,6 +10646,38 @@
       <c r="F52" t="inlineStr">
         <is>
           <t>Terresa (Agent-DF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D1/T1 数据质量残留登记（W9-35 立项）</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Sheet6（占位与重复行）+ 表外 T1_nodes v2.2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Z表 R23 + 本日志（V3.57 内原地补正，不升版）</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>域口径归一（W9-30/31/32）回读校验发现三项与域口径无关的数据质量残留：T1 三个废弃 L3 残留节点（VN-HRD-01/02、VN-THBOB-01）、Sheet6 空格占位 15 行、Sheet6 VN-BSRV-01 r125/r126 真重复。本批次不处理，合并立为清理任务 W9-35（Agent-DF，P2），在 Z 表 R23「H」项登记。本次仅新增登记行，价值节点数据无任何改动。</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Terresa (Agent-RC)</t>
         </is>
       </c>
     </row>
@@ -41701,7 +41729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -42191,6 +42219,28 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>H. D1/T1 数据质量残留</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>①T1_nodes v2.2 三个废弃 L3 残留节点：VN-HRD-01/02（L3-HRD）、VN-THBOB-01（L3-THBOB），两条 L3 监控表状态均为「❌已废弃-并入L3-JOPD」、PG dim_process 亦无，节点行仍在 T1，域列已按规则 C 留空；②D1 Sheet6 空格占位 15 行：VN-HR-11~14（关联交付物空）、VN-EQ-01（关联L4+L4名称空）、VN-MGA-01/02/03 与 VN-PAY-01/02/03/04/06/08/09（L4名称空）；③D1 Sheet6 VN-BSRV-01 r125/r126 真重复：L3/L4 完全相同，仅「关联交付物」一为《机构结算核对台账》含费用类型明细、一为简写。三项均系 2026-07-30 域口径归一（W9-30/31/32，交付清单批次012）回读校验中发现，与域口径无关，当批次未纳入范围。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>已合并为一条清理任务 W9-35（Agent-DF，P2），建议与 W9-29（拆分前旧 L3 名残留）同批处理。①需裁定去向：删行／改挂 L3-JOPD／保留并标废弃；②按 PG dim_process 回填或书面确认确无，其中 VN-PAY-08 与 W9-27（L3-EXP 未建立）重叠，回填前先确认 W9-27 进展；③需业务判断保留哪一侧后删另一行——注意本项属真重复，与本批已清理的 D2 旧 r36/r100、Sheet6 r137~r144 阶梯行成因不同（后者系一次错行写入的产物），不可套用同一处置。处理后须回写本行状态与 ★变更日志。</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Terresa + 架构组</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
